--- a/COMM1140/Tutorial Homework/Week 3 Tutorial Worksheet - Homework.xlsx
+++ b/COMM1140/Tutorial Homework/Week 3 Tutorial Worksheet - Homework.xlsx
@@ -6,17 +6,14 @@
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Tutorial Problem" sheetId="1" state="visible" r:id="rId4"/>
+    <sheet name="Tutorial Problem" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Transaction</t>
   </si>
@@ -75,31 +72,52 @@
     <t>#3</t>
   </si>
   <si>
+    <t>Profit</t>
+  </si>
+  <si>
     <t>#4</t>
   </si>
   <si>
     <t>#5</t>
   </si>
   <si>
+    <t>Dividends</t>
+  </si>
+  <si>
     <t>#6</t>
   </si>
   <si>
     <t>#7</t>
   </si>
   <si>
+    <t xml:space="preserve">Wages expense</t>
+  </si>
+  <si>
     <t>#8</t>
   </si>
   <si>
     <t>#9</t>
   </si>
   <si>
+    <t xml:space="preserve">Electricity expense</t>
+  </si>
+  <si>
     <t>#10</t>
   </si>
   <si>
+    <t xml:space="preserve">Supplies expense</t>
+  </si>
+  <si>
     <t>#11</t>
   </si>
   <si>
+    <t xml:space="preserve">Insurance expense</t>
+  </si>
+  <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liabilities + SE</t>
   </si>
 </sst>
 </file>
@@ -225,10 +243,10 @@
     <xf fontId="0" fillId="4" borderId="1" numFmtId="165" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="5" borderId="1" numFmtId="165" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="6" borderId="1" numFmtId="165" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="6" borderId="1" numFmtId="165" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="1" applyNumberFormat="1"/>
     <xf fontId="2" fillId="2" borderId="1" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="2" fillId="3" borderId="1" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="2" fillId="4" borderId="1" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="2" fillId="5" borderId="1" numFmtId="165" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -842,7 +860,9 @@
       <c r="A21" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="11"/>
+      <c r="B21" s="11">
+        <v>400000</v>
+      </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
@@ -851,7 +871,9 @@
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
-      <c r="K21" s="13"/>
+      <c r="K21" s="13">
+        <v>400000</v>
+      </c>
       <c r="L21" s="13"/>
       <c r="M21" s="14"/>
     </row>
@@ -860,11 +882,15 @@
         <v>17</v>
       </c>
       <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
+      <c r="C22" s="11">
+        <v>70000</v>
+      </c>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="12"/>
+      <c r="G22" s="12">
+        <v>70000</v>
+      </c>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
@@ -877,7 +903,9 @@
         <v>18</v>
       </c>
       <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
+      <c r="C23" s="11">
+        <v>-60000</v>
+      </c>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
@@ -893,7 +921,9 @@
       <c r="A24" s="10"/>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
+      <c r="D24" s="11">
+        <v>190000</v>
+      </c>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12"/>
@@ -901,16 +931,24 @@
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
       <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="14"/>
+      <c r="L24" s="13">
+        <v>130000</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" s="11"/>
+        <v>20</v>
+      </c>
+      <c r="B25" s="11">
+        <v>100000</v>
+      </c>
       <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="D25" s="11">
+        <v>-100000</v>
+      </c>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="12"/>
@@ -923,9 +961,11 @@
     </row>
     <row r="26">
       <c r="A26" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="11"/>
+        <v>21</v>
+      </c>
+      <c r="B26" s="11">
+        <v>-40000</v>
+      </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
@@ -935,19 +975,27 @@
       <c r="I26" s="12"/>
       <c r="J26" s="12"/>
       <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="14"/>
+      <c r="L26" s="13">
+        <v>-40000</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="11"/>
+        <v>23</v>
+      </c>
+      <c r="B27" s="11">
+        <v>-32000</v>
+      </c>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="12"/>
+      <c r="G27" s="12">
+        <v>-32000</v>
+      </c>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
@@ -957,33 +1005,46 @@
     </row>
     <row r="28">
       <c r="A28" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="11"/>
+        <v>24</v>
+      </c>
+      <c r="B28" s="11">
+        <v>-90000</v>
+      </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
+      <c r="H28" s="12">
+        <v>10000</v>
+      </c>
       <c r="I28" s="12"/>
       <c r="J28" s="12"/>
       <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="14"/>
+      <c r="L28" s="13">
+        <v>-100000</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="N28" s="16"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="11"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="11">
+        <v>70000</v>
+      </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
+      <c r="I29" s="12">
+        <v>70000</v>
+      </c>
       <c r="J29" s="12"/>
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
@@ -991,7 +1052,7 @@
     </row>
     <row r="30">
       <c r="A30" s="10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -1001,61 +1062,137 @@
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
+      <c r="J30" s="12">
+        <v>15000</v>
+      </c>
       <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="14"/>
+      <c r="L30" s="13">
+        <v>-15000</v>
+      </c>
+      <c r="M30" s="15" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
+      <c r="E31" s="11">
+        <v>800</v>
+      </c>
       <c r="F31" s="11"/>
-      <c r="G31" s="12"/>
+      <c r="G31" s="12">
+        <v>4000</v>
+      </c>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
       <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
-      <c r="M31" s="14"/>
+      <c r="L31" s="13">
+        <v>-3200</v>
+      </c>
+      <c r="M31" s="15" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="11"/>
+        <v>31</v>
+      </c>
+      <c r="B32" s="11">
+        <v>-24000</v>
+      </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
+      <c r="F32" s="11">
+        <v>6000</v>
+      </c>
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
       <c r="J32" s="12"/>
       <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="14"/>
+      <c r="L32" s="13">
+        <v>-18000</v>
+      </c>
+      <c r="M32" s="15" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
+      <c r="A33" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="18">
+        <f>SUM(B21:B32)</f>
+        <v>384000</v>
+      </c>
+      <c r="C33" s="18">
+        <f>SUM(C21:C32)</f>
+        <v>10000</v>
+      </c>
+      <c r="D33" s="18">
+        <f>SUM(D21:D32)</f>
+        <v>90000</v>
+      </c>
+      <c r="E33" s="18">
+        <f>SUM(E21:E32)</f>
+        <v>800</v>
+      </c>
+      <c r="F33" s="18">
+        <f>SUM(F21:F32)</f>
+        <v>6000</v>
+      </c>
+      <c r="G33" s="18">
+        <f>SUM(G21:G32)</f>
+        <v>42000</v>
+      </c>
+      <c r="H33" s="18">
+        <f>SUM(H21:H32)</f>
+        <v>10000</v>
+      </c>
+      <c r="I33" s="18">
+        <f>SUM(I21:I32)</f>
+        <v>70000</v>
+      </c>
+      <c r="J33" s="18">
+        <f>SUM(J21:J32)</f>
+        <v>15000</v>
+      </c>
+      <c r="K33" s="18">
+        <f>SUM(K21:K32)</f>
+        <v>400000</v>
+      </c>
+      <c r="L33" s="18">
+        <f>SUM(L21:L32)</f>
+        <v>-46200</v>
+      </c>
       <c r="M33" s="14"/>
+    </row>
+    <row r="36" ht="16.5">
+      <c r="A36" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="1">
+        <f>SUM(B21:F32)</f>
+        <v>490800</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5">
+      <c r="A37" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="1">
+        <f>SUM(G21:L32)</f>
+        <v>490800</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5">
+      <c r="A41" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="5">
